--- a/artfynd/A 17520-2022 artfynd.xlsx
+++ b/artfynd/A 17520-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17520-2022 artfynd.xlsx
+++ b/artfynd/A 17520-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68329125</v>
+        <v>68476394</v>
       </c>
       <c r="B2" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Malmslätt - Väst - Obj 225, Ög</t>
+          <t>Malmslätt - Obj 225, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529085.6534355392</v>
+        <v>529086</v>
       </c>
       <c r="R2" t="n">
-        <v>6474533.718875466</v>
+        <v>6474534</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,24 +743,14 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Granskog väster om Malmslätt. Bestånd 225 i Linköping kn skogsbruksplan.</t>
+          <t>Barrskog med enstaka lövträd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68476394</v>
+        <v>68329125</v>
       </c>
       <c r="B3" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Malmslätt - Obj 225, Ög</t>
+          <t>Malmslätt - Väst - Obj 225, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529085.6534355392</v>
+        <v>529086</v>
       </c>
       <c r="R3" t="n">
-        <v>6474533.718875466</v>
+        <v>6474534</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,24 +849,14 @@
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-09-05</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Barrskog med enstaka lövträd</t>
+          <t>Granskog väster om Malmslätt. Bestånd 225 i Linköping kn skogsbruksplan.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,6 +884,112 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>75249628</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58826</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Småvatten 60, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>529040</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6474608</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kärna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-04-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-08-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>För Linköpings kommun</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17520-2022 artfynd.xlsx
+++ b/artfynd/A 17520-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68476394</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Inventering av örtrika barrskogar i Linköpings kommun 2014-2017</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68329125</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,8 +1005,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75249628</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>